--- a/soho menu---.xlsx
+++ b/soho menu---.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10320"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E77C133-E557-1A41-8D92-53B830F32945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Documents\Pro2\menu4\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="288" yWindow="84" windowWidth="10452" windowHeight="8712" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
     <sheet name="ورقة2" sheetId="2" r:id="rId2"/>
     <sheet name="ورقة3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="134">
   <si>
     <t>الصنف</t>
   </si>
@@ -41,9 +45,6 @@
     <t>المشروبات الباردة</t>
   </si>
   <si>
-    <t>مياه معدنيه فلو</t>
-  </si>
-  <si>
     <t>مياه فواره</t>
   </si>
   <si>
@@ -401,16 +402,46 @@
     <t>قطعة برجر تقدم مع الخس والطماطم وشريحة الجبن فى لقمة كيزر مع البطاطس المقلية مع عصير كيدز</t>
   </si>
   <si>
-    <t>سلطة الخس وشرائح التورتيلا مع الدجاج المشوى وقطع البيكون والجبنة المكس مغطاة برانش صوص والذرة والفاصولياء الحمراء مع البيكوديجالو</t>
-  </si>
-  <si>
     <t>ستيك ساندوتش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مياه معدنيه </t>
+  </si>
+  <si>
+    <t>بريسكت ناتشوز</t>
+  </si>
+  <si>
+    <t>اضافه جديده مكوناتها.. ناتشوز+لحمة بريسكت+تشيز+هلابينو+كورن+فاصوليا حمراء+صور كريم</t>
+  </si>
+  <si>
+    <t>سلطة الخس وشرائح التورتيلا مع الدجاج المشوى وقطع البيكون والجبنة المكس مغطاة  والذرة والفاصولياء الحمراء مع البيكوديجالو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرائح دجاج متبلة مع خضار مشوى تقدم فى تورتيلا مقرمشة ومحشية بخليط من الجبن الذائبة </t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرائح بيف متبلة مع خضار مشوى تقدم فى تورتيلا مقرمشة ومحشية بخليط من الجبن الذائبة </t>
+  </si>
+  <si>
+    <t xml:space="preserve">قطع جمبرى متبلة مع خضار مشوى تقدم فى تورتيلا مقرمشة ومحشية بخليط من الجبن الذائبة </t>
+  </si>
+  <si>
+    <t xml:space="preserve">قطع دجاج وبيف وجمبرى مع الفلفل والبصل تقدم مع ارز وخبز التورتيلا </t>
+  </si>
+  <si>
+    <t xml:space="preserve">قطع اللحم مشوى مع البصل والفلفل تقدم مع ارز وخبز التورتيلا  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">قطع دجاج مشوى مع البصل والفلفل تقدم مع ارز وخبز التورتيلا  </t>
+  </si>
+  <si>
+    <t>كنترى فرايد تشيكن</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -730,7 +761,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -756,10 +787,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -771,19 +820,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -792,18 +829,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Comma 2 2" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -819,9 +851,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -859,9 +891,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -896,7 +928,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -931,7 +963,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1104,15 +1136,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L113"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="62.8203125" customWidth="1"/>
-    <col min="2" max="2" width="8.33984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="62.85546875" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1130,816 +1162,822 @@
       <c r="K1" s="4"/>
       <c r="L1" s="5"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B2" s="21"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="B3" s="7">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="8">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="8">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="8">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="8">
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B9" s="18"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="B10" s="8">
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="8">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="18"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B15" s="25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="27"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="17">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="17"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="24"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="17">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="17"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="17">
         <v>169</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="20"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="19">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="17">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="17"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="17">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="17"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="17">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="17"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="17">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="17"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="17">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="17"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="24"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="17">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="17"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="17">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="17"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="17">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="17"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="17">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="17"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" s="17">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="17"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="17">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="17"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" s="17">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="17"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="17">
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="21"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="22">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="17"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="17">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="17"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="17">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" s="17"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="17">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="17"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="17">
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="22"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="26"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="22">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="17"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59" s="17">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="17"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="17"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B62" s="17"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" s="17">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" s="17"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="24"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B66" s="17">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B67" s="17"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="17">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B69" s="17"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="17">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B71" s="17"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B72" s="24"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="17">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B74" s="17"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" s="17">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B76" s="17"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="17">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" s="17"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B79" s="17">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B80" s="17"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B81" s="17">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" s="17"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B83" s="17">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B84" s="18"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B85" s="19"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B86" s="24"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="17">
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="22"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="22">
-        <v>169</v>
-      </c>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="D23" s="12"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="22">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="22"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" s="22">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="22"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="22">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="22"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="22">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="22"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="22">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="22"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="26"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="22">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="22"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37" s="22">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="22"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="22">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B40" s="22"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="22">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B42" s="22"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="22">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B44" s="22"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B45" s="22">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B46" s="22"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="22">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" s="22"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B49" s="22">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B50" s="22"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="22">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B52" s="22"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B53" s="22">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B54" s="22"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B55" s="22">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B56" s="22"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" s="22">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" s="22"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B59" s="22">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B60" s="22"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B61" s="22">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B62" s="22"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B63" s="26"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B64" s="22">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B65" s="22"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B66" s="22">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="16" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="B67" s="22"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B68" s="22">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B69" s="22"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="26"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="22">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B72" s="22"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="22">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B74" s="22"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="22">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="B76" s="22"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="22">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B78" s="22"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="22">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B80" s="22"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="22">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B82" s="29"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="B83" s="30"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="26"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="11" t="s">
+      <c r="B88" s="17"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B85" s="22">
+      <c r="B89" s="17">
         <v>189</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="13" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B86" s="22"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="11" t="s">
+      <c r="B90" s="17"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B87" s="22">
+      <c r="B91" s="17">
         <v>189</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="13" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="22"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="11" t="s">
+      <c r="B92" s="17"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B89" s="22">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B90" s="22"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="17" t="s">
+      <c r="B93" s="30"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B91" s="28"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B92" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B93" s="8">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="B94" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B95" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B96" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B97" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B98" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B99" s="8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B100" s="8">
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B98" s="8">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="23" t="s">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B101" s="28"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="B99" s="23"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B100" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B101" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="B102" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B103" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B104" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B105" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B106" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B107" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="17" t="s">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B108" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B109" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B110" s="23"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B108" s="18"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B109" s="8">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B110" s="8">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="B111" s="8">
         <v>130</v>
       </c>
     </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B112" s="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B113" s="8">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B53:B54"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A19:B19"/>
@@ -1950,22 +1988,28 @@
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="A85:B85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
@@ -1973,321 +2017,321 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.48046875" customWidth="1"/>
+    <col min="1" max="1" width="54.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2296,9 +2340,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
